--- a/3-能力管理/运行记录类文件/TXHS-03-06-2025年度运维服务能力指标完成情况.xlsx
+++ b/3-能力管理/运行记录类文件/TXHS-03-06-2025年度运维服务能力指标完成情况.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9575"/>
+    <workbookView windowWidth="21228" windowHeight="7787"/>
   </bookViews>
   <sheets>
     <sheet name="KPI指标体系" sheetId="1" r:id="rId1"/>
@@ -3256,7 +3256,10 @@
       </c>
     </row>
     <row r="31" spans="1:19">
-      <c r="A31" s="7"/>
+      <c r="A31" s="7">
+        <f>ROW()-2</f>
+        <v>29</v>
+      </c>
       <c r="B31" s="8"/>
       <c r="C31" s="16" t="s">
         <v>77</v>
@@ -3311,7 +3314,10 @@
       </c>
     </row>
     <row r="32" spans="1:19">
-      <c r="A32" s="7"/>
+      <c r="A32" s="7">
+        <f>ROW()-2</f>
+        <v>30</v>
+      </c>
       <c r="B32" s="8"/>
       <c r="C32" s="17"/>
       <c r="D32" s="9" t="s">

--- a/3-能力管理/运行记录类文件/TXHS-03-06-2025年度运维服务能力指标完成情况.xlsx
+++ b/3-能力管理/运行记录类文件/TXHS-03-06-2025年度运维服务能力指标完成情况.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21228" windowHeight="7787"/>
+    <workbookView windowWidth="28515" windowHeight="12315"/>
   </bookViews>
   <sheets>
     <sheet name="KPI指标体系" sheetId="1" r:id="rId1"/>
@@ -452,7 +452,7 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -488,6 +488,13 @@
       <sz val="11"/>
       <name val="宋体"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1000,65 +1007,65 @@
     </border>
   </borders>
   <cellStyleXfs count="55">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" applyNumberFormat="0" applyFont="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="7" applyNumberFormat="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="8" applyNumberFormat="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="7" applyNumberFormat="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="9" applyNumberFormat="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" applyNumberFormat="0" applyFont="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="7" applyNumberFormat="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="8" applyNumberFormat="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="7" applyNumberFormat="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="9" applyNumberFormat="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="25" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="25" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="42" fontId="25" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="25" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="25" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="26" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="26" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="26" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="26" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="26" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyAlignment="1">
@@ -1523,18 +1530,18 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:S38"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
     <col min="2" max="2" width="4.75" style="2" customWidth="1"/>
     <col min="3" max="3" width="10.75" style="2" customWidth="1"/>
     <col min="4" max="4" width="21" style="2" customWidth="1"/>
-    <col min="5" max="5" width="8.62962962962963" style="2" customWidth="1"/>
-    <col min="6" max="6" width="6.77777777777778" style="2" customWidth="1"/>
-    <col min="7" max="10" width="11.6296296296296" style="2" customWidth="1"/>
-    <col min="11" max="15" width="11.6296296296296" style="2"/>
-    <col min="16" max="17" width="12.8796296296296" style="2"/>
-    <col min="18" max="18" width="12.8888888888889" style="1"/>
+    <col min="5" max="5" width="8.625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="6.75" style="2" customWidth="1"/>
+    <col min="7" max="10" width="11.625" style="2" customWidth="1"/>
+    <col min="11" max="15" width="11.625" style="2"/>
+    <col min="16" max="17" width="12.875" style="2"/>
+    <col min="18" max="18" width="12.875" style="1"/>
     <col min="19" max="19" width="9.5" style="1"/>
     <col min="20" max="16384" width="9" style="2"/>
   </cols>
@@ -1678,7 +1685,7 @@
         <v>0.982</v>
       </c>
     </row>
-    <row r="4" spans="1:19">
+    <row r="4" ht="14.25" spans="1:19">
       <c r="A4" s="7">
         <f t="shared" ref="A4:A13" si="0">ROW()-2</f>
         <v>2</v>
@@ -1734,7 +1741,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:19">
+    <row r="5" ht="14.25" spans="1:19">
       <c r="A5" s="7">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -1790,7 +1797,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:19">
+    <row r="6" ht="14.25" spans="1:19">
       <c r="A6" s="7">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -1846,7 +1853,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:19">
+    <row r="7" ht="14.25" spans="1:19">
       <c r="A7" s="7">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -1902,12 +1909,12 @@
       <c r="R7" s="10">
         <v>1</v>
       </c>
-      <c r="S7" s="13" cm="1">
+      <c r="S7" s="13">
         <f t="array" ref="S7">SUMPRODUCT(--(0&amp;SUBSTITUTE(G7:R7,"-","0")))/IF(F7="季度",4,IF(F7="月度",12,1))</f>
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:19">
+    <row r="8" ht="14.25" spans="1:19">
       <c r="A8" s="7">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -1961,12 +1968,12 @@
       <c r="R8" s="10">
         <v>1</v>
       </c>
-      <c r="S8" s="13" cm="1">
+      <c r="S8" s="13">
         <f t="array" ref="S8">SUMPRODUCT(--(0&amp;SUBSTITUTE(G8:R8,"-","0")))/IF(F8="季度",4,IF(F8="月度",12,1))</f>
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:19">
+    <row r="9" ht="14.25" spans="1:19">
       <c r="A9" s="7">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -2020,12 +2027,12 @@
       <c r="R9" s="10">
         <v>1</v>
       </c>
-      <c r="S9" s="13" cm="1">
+      <c r="S9" s="13">
         <f t="array" ref="S9">SUMPRODUCT(--(0&amp;SUBSTITUTE(G9:R9,"-","0")))/IF(F9="季度",4,IF(F9="月度",12,1))</f>
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:19">
+    <row r="10" ht="14.25" spans="1:19">
       <c r="A10" s="7">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -2079,12 +2086,12 @@
       <c r="R10" s="10">
         <v>1</v>
       </c>
-      <c r="S10" s="13" cm="1">
+      <c r="S10" s="13">
         <f t="array" ref="S10">SUMPRODUCT(--(0&amp;SUBSTITUTE(G10:R10,"-","0")))/IF(F10="季度",4,IF(F10="月度",12,1))</f>
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:19">
+    <row r="11" ht="14.25" spans="1:19">
       <c r="A11" s="7">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -2138,12 +2145,12 @@
       <c r="R11" s="10">
         <v>1</v>
       </c>
-      <c r="S11" s="13" cm="1">
+      <c r="S11" s="13">
         <f t="array" ref="S11">SUMPRODUCT(--(0&amp;SUBSTITUTE(G11:R11,"-","0")))/IF(F11="季度",4,IF(F11="月度",12,1))</f>
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:19">
+    <row r="12" ht="14.25" spans="1:19">
       <c r="A12" s="7">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -2197,12 +2204,12 @@
       <c r="R12" s="10">
         <v>1</v>
       </c>
-      <c r="S12" s="13" cm="1">
+      <c r="S12" s="13">
         <f t="array" ref="S12">SUMPRODUCT(--(0&amp;SUBSTITUTE(G12:R12,"-","0")))/IF(F12="季度",4,IF(F12="月度",12,1))</f>
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:19">
+    <row r="13" ht="14.25" spans="1:19">
       <c r="A13" s="7">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -2262,7 +2269,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="14" spans="1:19">
+    <row r="14" ht="14.25" spans="1:19">
       <c r="A14" s="7">
         <f t="shared" ref="A14:A23" si="1">ROW()-2</f>
         <v>12</v>
@@ -2316,12 +2323,12 @@
       <c r="R14" s="10">
         <v>1</v>
       </c>
-      <c r="S14" s="13" cm="1">
+      <c r="S14" s="13">
         <f t="array" ref="S14">SUMPRODUCT(--(0&amp;SUBSTITUTE(G14:R14,"-","0")))/IF(F14="季度",4,IF(F14="月度",12,1))</f>
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:19">
+    <row r="15" ht="14.25" spans="1:19">
       <c r="A15" s="7">
         <f t="shared" si="1"/>
         <v>13</v>
@@ -2375,12 +2382,12 @@
       <c r="R15" s="10">
         <v>1</v>
       </c>
-      <c r="S15" s="13" cm="1">
+      <c r="S15" s="13">
         <f t="array" ref="S15">SUMPRODUCT(--(0&amp;SUBSTITUTE(G15:R15,"-","0")))/IF(F15="季度",4,IF(F15="月度",12,1))</f>
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:19">
+    <row r="16" ht="14.25" spans="1:19">
       <c r="A16" s="7">
         <f t="shared" si="1"/>
         <v>14</v>
@@ -2434,12 +2441,12 @@
       <c r="R16" s="10">
         <v>1</v>
       </c>
-      <c r="S16" s="13" cm="1">
+      <c r="S16" s="13">
         <f t="array" ref="S16">SUMPRODUCT(--(0&amp;SUBSTITUTE(G16:R16,"-","0")))/IF(F16="季度",4,IF(F16="月度",12,1))</f>
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:19">
+    <row r="17" ht="14.25" spans="1:19">
       <c r="A17" s="7">
         <f t="shared" si="1"/>
         <v>15</v>
@@ -2491,12 +2498,12 @@
       <c r="R17" s="10">
         <v>1</v>
       </c>
-      <c r="S17" s="13" cm="1">
+      <c r="S17" s="13">
         <f t="array" ref="S17">SUMPRODUCT(--(0&amp;SUBSTITUTE(G17:R17,"-","0")))/IF(F17="季度",4,IF(F17="月度",12,1))</f>
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:19">
+    <row r="18" ht="14.25" spans="1:19">
       <c r="A18" s="7">
         <f t="shared" si="1"/>
         <v>16</v>
@@ -2550,12 +2557,12 @@
       <c r="R18" s="10">
         <v>1</v>
       </c>
-      <c r="S18" s="13" cm="1">
+      <c r="S18" s="13">
         <f t="array" ref="S18">SUMPRODUCT(--(0&amp;SUBSTITUTE(G18:R18,"-","0")))/IF(F18="季度",4,IF(F18="月度",12,1))</f>
         <v>0.955</v>
       </c>
     </row>
-    <row r="19" spans="1:19">
+    <row r="19" ht="14.25" spans="1:19">
       <c r="A19" s="7">
         <f t="shared" si="1"/>
         <v>17</v>
@@ -2607,12 +2614,12 @@
       <c r="R19" s="10">
         <v>1</v>
       </c>
-      <c r="S19" s="13" cm="1">
+      <c r="S19" s="13">
         <f t="array" ref="S19">SUMPRODUCT(--(0&amp;SUBSTITUTE(G19:R19,"-","0")))/IF(F19="季度",4,IF(F19="月度",12,1))</f>
         <v>0.975</v>
       </c>
     </row>
-    <row r="20" spans="1:19">
+    <row r="20" ht="14.25" spans="1:19">
       <c r="A20" s="7">
         <f t="shared" si="1"/>
         <v>18</v>
@@ -2670,7 +2677,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:19">
+    <row r="21" ht="14.25" spans="1:19">
       <c r="A21" s="7">
         <f t="shared" si="1"/>
         <v>19</v>
@@ -2724,12 +2731,12 @@
       <c r="R21" s="10">
         <v>1</v>
       </c>
-      <c r="S21" s="13" cm="1">
+      <c r="S21" s="13">
         <f t="array" ref="S21">SUMPRODUCT(--(0&amp;SUBSTITUTE(G21:R21,"-","0")))/IF(F21="季度",4,IF(F21="月度",12,1))</f>
         <v>0.990833333333333</v>
       </c>
     </row>
-    <row r="22" spans="1:19">
+    <row r="22" ht="14.25" spans="1:19">
       <c r="A22" s="7">
         <f t="shared" si="1"/>
         <v>20</v>
@@ -2783,12 +2790,12 @@
       <c r="R22" s="10">
         <v>1</v>
       </c>
-      <c r="S22" s="13" cm="1">
+      <c r="S22" s="13">
         <f t="array" ref="S22">SUMPRODUCT(--(0&amp;SUBSTITUTE(G22:R22,"-","0")))/IF(F22="季度",4,IF(F22="月度",12,1))</f>
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:19">
+    <row r="23" ht="14.25" spans="1:19">
       <c r="A23" s="7">
         <f t="shared" si="1"/>
         <v>21</v>
@@ -2842,14 +2849,14 @@
       <c r="R23" s="10">
         <v>1</v>
       </c>
-      <c r="S23" s="13" cm="1">
+      <c r="S23" s="13">
         <f t="array" ref="S23">SUMPRODUCT(--(0&amp;SUBSTITUTE(G23:R23,"-","0")))/IF(F23="季度",4,IF(F23="月度",12,1))</f>
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:19">
+    <row r="24" ht="14.25" spans="1:19">
       <c r="A24" s="7">
-        <f t="shared" ref="A24:A35" si="2">ROW()-2</f>
+        <f t="shared" ref="A24:A37" si="2">ROW()-2</f>
         <v>22</v>
       </c>
       <c r="B24" s="8"/>
@@ -2903,7 +2910,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="25" spans="1:19">
+    <row r="25" ht="14.25" spans="1:19">
       <c r="A25" s="7">
         <f t="shared" si="2"/>
         <v>23</v>
@@ -2961,7 +2968,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:19">
+    <row r="26" ht="14.25" spans="1:19">
       <c r="A26" s="7">
         <f t="shared" si="2"/>
         <v>24</v>
@@ -3019,7 +3026,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="1:19">
+    <row r="27" ht="14.25" spans="1:19">
       <c r="A27" s="7">
         <f t="shared" si="2"/>
         <v>25</v>
@@ -3073,12 +3080,12 @@
       <c r="R27" s="10">
         <v>1</v>
       </c>
-      <c r="S27" s="13" cm="1">
+      <c r="S27" s="13">
         <f t="array" ref="S27">SUMPRODUCT(--(0&amp;SUBSTITUTE(G27:R27,"-","0")))/IF(F27="季度",4,IF(F27="月度",12,1))</f>
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:19">
+    <row r="28" ht="14.25" spans="1:19">
       <c r="A28" s="7">
         <f t="shared" si="2"/>
         <v>26</v>
@@ -3130,12 +3137,12 @@
       <c r="R28" s="10">
         <v>1</v>
       </c>
-      <c r="S28" s="13" cm="1">
+      <c r="S28" s="13">
         <f t="array" ref="S28">SUMPRODUCT(--(0&amp;SUBSTITUTE(G28:R28,"-","0")))/IF(F28="季度",4,IF(F28="月度",12,1))</f>
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:19">
+    <row r="29" ht="14.25" spans="1:19">
       <c r="A29" s="7">
         <f t="shared" si="2"/>
         <v>27</v>
@@ -3191,12 +3198,12 @@
       <c r="R29" s="10">
         <v>1</v>
       </c>
-      <c r="S29" s="13" cm="1">
+      <c r="S29" s="13">
         <f t="array" ref="S29">SUMPRODUCT(--(0&amp;SUBSTITUTE(G29:R29,"-","0")))/IF(F29="季度",4,IF(F29="月度",12,1))</f>
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:19">
+    <row r="30" ht="14.25" spans="1:19">
       <c r="A30" s="7">
         <f t="shared" si="2"/>
         <v>28</v>
@@ -3257,7 +3264,7 @@
     </row>
     <row r="31" spans="1:19">
       <c r="A31" s="7">
-        <f>ROW()-2</f>
+        <f t="shared" si="2"/>
         <v>29</v>
       </c>
       <c r="B31" s="8"/>
@@ -3313,9 +3320,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:19">
+    <row r="32" ht="14.25" spans="1:19">
       <c r="A32" s="7">
-        <f>ROW()-2</f>
+        <f t="shared" si="2"/>
         <v>30</v>
       </c>
       <c r="B32" s="8"/>
@@ -3365,14 +3372,14 @@
       <c r="R32" s="10">
         <v>1</v>
       </c>
-      <c r="S32" s="13" cm="1">
+      <c r="S32" s="13">
         <f t="array" ref="S32">SUMPRODUCT(--(0&amp;SUBSTITUTE(G32:R32,"-","0")))/IF(F32="季度",4,IF(F32="月度",12,1))</f>
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:19">
+    <row r="33" ht="14.25" spans="1:19">
       <c r="A33" s="7">
-        <f>ROW()-2</f>
+        <f t="shared" si="2"/>
         <v>31</v>
       </c>
       <c r="B33" s="8"/>
@@ -3430,7 +3437,7 @@
     </row>
     <row r="34" ht="16" customHeight="1" spans="1:19">
       <c r="A34" s="7">
-        <f>ROW()-2</f>
+        <f t="shared" si="2"/>
         <v>32</v>
       </c>
       <c r="B34" s="8"/>
@@ -3486,9 +3493,9 @@
         <v>19</v>
       </c>
     </row>
-    <row r="35" spans="1:19">
+    <row r="35" ht="14.25" spans="1:19">
       <c r="A35" s="7">
-        <f>ROW()-2</f>
+        <f t="shared" si="2"/>
         <v>33</v>
       </c>
       <c r="B35" s="8"/>
@@ -3544,9 +3551,9 @@
         <v>94</v>
       </c>
     </row>
-    <row r="36" spans="1:19">
+    <row r="36" ht="14.25" spans="1:19">
       <c r="A36" s="7">
-        <f>ROW()-2</f>
+        <f t="shared" si="2"/>
         <v>34</v>
       </c>
       <c r="B36" s="8" t="s">
@@ -3598,14 +3605,14 @@
       <c r="R36" s="10">
         <v>1</v>
       </c>
-      <c r="S36" s="13" cm="1">
+      <c r="S36" s="13">
         <f t="array" ref="S36">SUMPRODUCT(--(0&amp;SUBSTITUTE(G36:R36,"-","0")))/IF(F36="季度",4,IF(F36="月度",12,1))</f>
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:19">
+    <row r="37" ht="14.25" spans="1:19">
       <c r="A37" s="7">
-        <f>ROW()-2</f>
+        <f t="shared" si="2"/>
         <v>35</v>
       </c>
       <c r="B37" s="8" t="s">

--- a/3-能力管理/运行记录类文件/TXHS-03-06-2025年度运维服务能力指标完成情况.xlsx
+++ b/3-能力管理/运行记录类文件/TXHS-03-06-2025年度运维服务能力指标完成情况.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28515" windowHeight="12315"/>
+    <workbookView windowWidth="22188" windowHeight="9575"/>
   </bookViews>
   <sheets>
     <sheet name="KPI指标体系" sheetId="1" r:id="rId1"/>
@@ -27,28 +27,6 @@
     </ext>
   </extLst>
 </workbook>
-</file>
-
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1530,18 +1508,18 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:S38"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
     <col min="2" max="2" width="4.75" style="2" customWidth="1"/>
     <col min="3" max="3" width="10.75" style="2" customWidth="1"/>
     <col min="4" max="4" width="21" style="2" customWidth="1"/>
-    <col min="5" max="5" width="8.625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="8.62962962962963" style="2" customWidth="1"/>
     <col min="6" max="6" width="6.75" style="2" customWidth="1"/>
-    <col min="7" max="10" width="11.625" style="2" customWidth="1"/>
-    <col min="11" max="15" width="11.625" style="2"/>
-    <col min="16" max="17" width="12.875" style="2"/>
-    <col min="18" max="18" width="12.875" style="1"/>
+    <col min="7" max="10" width="11.6296296296296" style="2" customWidth="1"/>
+    <col min="11" max="15" width="11.6296296296296" style="2"/>
+    <col min="16" max="17" width="12.8796296296296" style="2"/>
+    <col min="18" max="18" width="12.8796296296296" style="1"/>
     <col min="19" max="19" width="9.5" style="1"/>
     <col min="20" max="16384" width="9" style="2"/>
   </cols>
@@ -1626,7 +1604,7 @@
       </c>
       <c r="S2" s="5"/>
     </row>
-    <row r="3" spans="1:19">
+    <row r="3" ht="28.8" spans="1:19">
       <c r="A3" s="7">
         <f>ROW()-2</f>
         <v>1</v>
@@ -1685,7 +1663,7 @@
         <v>0.982</v>
       </c>
     </row>
-    <row r="4" ht="14.25" spans="1:19">
+    <row r="4" spans="1:19">
       <c r="A4" s="7">
         <f t="shared" ref="A4:A13" si="0">ROW()-2</f>
         <v>2</v>
@@ -1741,7 +1719,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" ht="14.25" spans="1:19">
+    <row r="5" spans="1:19">
       <c r="A5" s="7">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -1797,7 +1775,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" ht="14.25" spans="1:19">
+    <row r="6" spans="1:19">
       <c r="A6" s="7">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -1853,7 +1831,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" ht="14.25" spans="1:19">
+    <row r="7" spans="1:19">
       <c r="A7" s="7">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -1914,7 +1892,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" ht="14.25" spans="1:19">
+    <row r="8" spans="1:19">
       <c r="A8" s="7">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -1973,7 +1951,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" ht="14.25" spans="1:19">
+    <row r="9" spans="1:19">
       <c r="A9" s="7">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -2032,7 +2010,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" ht="14.25" spans="1:19">
+    <row r="10" spans="1:19">
       <c r="A10" s="7">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -2091,7 +2069,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" ht="14.25" spans="1:19">
+    <row r="11" spans="1:19">
       <c r="A11" s="7">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -2150,7 +2128,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" ht="14.25" spans="1:19">
+    <row r="12" spans="1:19">
       <c r="A12" s="7">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -2209,7 +2187,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" ht="14.25" spans="1:19">
+    <row r="13" spans="1:19">
       <c r="A13" s="7">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -2269,7 +2247,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="14" ht="14.25" spans="1:19">
+    <row r="14" spans="1:19">
       <c r="A14" s="7">
         <f t="shared" ref="A14:A23" si="1">ROW()-2</f>
         <v>12</v>
@@ -2328,7 +2306,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" ht="14.25" spans="1:19">
+    <row r="15" spans="1:19">
       <c r="A15" s="7">
         <f t="shared" si="1"/>
         <v>13</v>
@@ -2387,7 +2365,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" ht="14.25" spans="1:19">
+    <row r="16" spans="1:19">
       <c r="A16" s="7">
         <f t="shared" si="1"/>
         <v>14</v>
@@ -2446,7 +2424,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" ht="14.25" spans="1:19">
+    <row r="17" spans="1:19">
       <c r="A17" s="7">
         <f t="shared" si="1"/>
         <v>15</v>
@@ -2503,7 +2481,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" ht="14.25" spans="1:19">
+    <row r="18" spans="1:19">
       <c r="A18" s="7">
         <f t="shared" si="1"/>
         <v>16</v>
@@ -2562,7 +2540,7 @@
         <v>0.955</v>
       </c>
     </row>
-    <row r="19" ht="14.25" spans="1:19">
+    <row r="19" spans="1:19">
       <c r="A19" s="7">
         <f t="shared" si="1"/>
         <v>17</v>
@@ -2619,7 +2597,7 @@
         <v>0.975</v>
       </c>
     </row>
-    <row r="20" ht="14.25" spans="1:19">
+    <row r="20" spans="1:19">
       <c r="A20" s="7">
         <f t="shared" si="1"/>
         <v>18</v>
@@ -2677,7 +2655,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" ht="14.25" spans="1:19">
+    <row r="21" spans="1:19">
       <c r="A21" s="7">
         <f t="shared" si="1"/>
         <v>19</v>
@@ -2736,7 +2714,7 @@
         <v>0.990833333333333</v>
       </c>
     </row>
-    <row r="22" ht="14.25" spans="1:19">
+    <row r="22" spans="1:19">
       <c r="A22" s="7">
         <f t="shared" si="1"/>
         <v>20</v>
@@ -2795,7 +2773,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" ht="14.25" spans="1:19">
+    <row r="23" spans="1:19">
       <c r="A23" s="7">
         <f t="shared" si="1"/>
         <v>21</v>
@@ -2854,7 +2832,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" ht="14.25" spans="1:19">
+    <row r="24" spans="1:19">
       <c r="A24" s="7">
         <f t="shared" ref="A24:A37" si="2">ROW()-2</f>
         <v>22</v>
@@ -2910,7 +2888,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="25" ht="14.25" spans="1:19">
+    <row r="25" spans="1:19">
       <c r="A25" s="7">
         <f t="shared" si="2"/>
         <v>23</v>
@@ -2968,7 +2946,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" ht="14.25" spans="1:19">
+    <row r="26" spans="1:19">
       <c r="A26" s="7">
         <f t="shared" si="2"/>
         <v>24</v>
@@ -3026,7 +3004,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" ht="14.25" spans="1:19">
+    <row r="27" spans="1:19">
       <c r="A27" s="7">
         <f t="shared" si="2"/>
         <v>25</v>
@@ -3085,7 +3063,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" ht="14.25" spans="1:19">
+    <row r="28" spans="1:19">
       <c r="A28" s="7">
         <f t="shared" si="2"/>
         <v>26</v>
@@ -3142,7 +3120,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" ht="14.25" spans="1:19">
+    <row r="29" spans="1:19">
       <c r="A29" s="7">
         <f t="shared" si="2"/>
         <v>27</v>
@@ -3203,7 +3181,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" ht="14.25" spans="1:19">
+    <row r="30" spans="1:19">
       <c r="A30" s="7">
         <f t="shared" si="2"/>
         <v>28</v>
@@ -3257,7 +3235,7 @@
       <c r="R30" s="10">
         <v>1</v>
       </c>
-      <c r="S30" s="13" cm="1">
+      <c r="S30" s="13">
         <f t="array" ref="S30">SUMPRODUCT(--(0&amp;SUBSTITUTE(G30:R30,"-","0")))/IF(F30="季度",4,IF(F30="月度",12,1))</f>
         <v>0.9425</v>
       </c>
@@ -3320,7 +3298,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" ht="14.25" spans="1:19">
+    <row r="32" spans="1:19">
       <c r="A32" s="7">
         <f t="shared" si="2"/>
         <v>30</v>
@@ -3377,7 +3355,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" ht="14.25" spans="1:19">
+    <row r="33" spans="1:19">
       <c r="A33" s="7">
         <f t="shared" si="2"/>
         <v>31</v>
@@ -3493,7 +3471,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="35" ht="14.25" spans="1:19">
+    <row r="35" spans="1:19">
       <c r="A35" s="7">
         <f t="shared" si="2"/>
         <v>33</v>
@@ -3551,7 +3529,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="36" ht="14.25" spans="1:19">
+    <row r="36" spans="1:19">
       <c r="A36" s="7">
         <f t="shared" si="2"/>
         <v>34</v>
@@ -3610,7 +3588,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" ht="14.25" spans="1:19">
+    <row r="37" spans="1:19">
       <c r="A37" s="7">
         <f t="shared" si="2"/>
         <v>35</v>
